--- a/Діаграма_Ганта.xlsx
+++ b/Діаграма_Ганта.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Діаграма Ганта" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Ключові віхи" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Помісячний план" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -68,12 +69,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -112,13 +113,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -486,775 +497,2268 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG18"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="6" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="6" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="6" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="6" customWidth="1" min="23" max="23"/>
-    <col width="6" customWidth="1" min="24" max="24"/>
-    <col width="6" customWidth="1" min="25" max="25"/>
-    <col width="6" customWidth="1" min="26" max="26"/>
-    <col width="6" customWidth="1" min="27" max="27"/>
-    <col width="6" customWidth="1" min="28" max="28"/>
-    <col width="6" customWidth="1" min="29" max="29"/>
-    <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="6" customWidth="1" min="31" max="31"/>
-    <col width="6" customWidth="1" min="32" max="32"/>
-    <col width="6" customWidth="1" min="33" max="33"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="5.5" customWidth="1" min="11" max="11"/>
+    <col width="5.5" customWidth="1" min="12" max="12"/>
+    <col width="5.5" customWidth="1" min="13" max="13"/>
+    <col width="5.5" customWidth="1" min="14" max="14"/>
+    <col width="5.5" customWidth="1" min="15" max="15"/>
+    <col width="5.5" customWidth="1" min="16" max="16"/>
+    <col width="5.5" customWidth="1" min="17" max="17"/>
+    <col width="5.5" customWidth="1" min="18" max="18"/>
+    <col width="5.5" customWidth="1" min="19" max="19"/>
+    <col width="5.5" customWidth="1" min="20" max="20"/>
+    <col width="5.5" customWidth="1" min="21" max="21"/>
+    <col width="5.5" customWidth="1" min="22" max="22"/>
+    <col width="5.5" customWidth="1" min="23" max="23"/>
+    <col width="5.5" customWidth="1" min="24" max="24"/>
+    <col width="5.5" customWidth="1" min="25" max="25"/>
+    <col width="5.5" customWidth="1" min="26" max="26"/>
+    <col width="5.5" customWidth="1" min="27" max="27"/>
+    <col width="5.5" customWidth="1" min="28" max="28"/>
+    <col width="5.5" customWidth="1" min="29" max="29"/>
+    <col width="5.5" customWidth="1" min="30" max="30"/>
+    <col width="5.5" customWidth="1" min="31" max="31"/>
+    <col width="5.5" customWidth="1" min="32" max="32"/>
+    <col width="5.5" customWidth="1" min="33" max="33"/>
+    <col width="5.5" customWidth="1" min="34" max="34"/>
+    <col width="5.5" customWidth="1" min="35" max="35"/>
+    <col width="5.5" customWidth="1" min="36" max="36"/>
+    <col width="5.5" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Дорожня карта відкриття фізичного магазину footballshop.com.ua (2026)</t>
+          <t>Дорожня карта відкриття фізичного магазину footballshop.com.ua (2026) — детальний план</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>Етап</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Завдання</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Початок</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Кінець</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Днів</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Відповідальний</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Бюджет, грн</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Очікуваний результат</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>01.06</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>08.06</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>15.06</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>22.06</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>29.06</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>06.07</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>13.07</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>20.07</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>27.07</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>03.08</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>10.08</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>17.08</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>24.08</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>31.08</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>07.09</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>14.09</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>21.09</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>28.09</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>05.10</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="AD3" s="2" t="inlineStr">
         <is>
           <t>12.10</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AE3" s="2" t="inlineStr">
         <is>
           <t>19.10</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
+      <c r="AF3" s="2" t="inlineStr">
         <is>
           <t>26.10</t>
         </is>
       </c>
-      <c r="AC3" s="2" t="inlineStr">
+      <c r="AG3" s="2" t="inlineStr">
         <is>
           <t>02.11</t>
         </is>
       </c>
-      <c r="AD3" s="2" t="inlineStr">
+      <c r="AH3" s="2" t="inlineStr">
         <is>
           <t>09.11</t>
         </is>
       </c>
-      <c r="AE3" s="2" t="inlineStr">
+      <c r="AI3" s="2" t="inlineStr">
         <is>
           <t>16.11</t>
         </is>
       </c>
-      <c r="AF3" s="2" t="inlineStr">
+      <c r="AJ3" s="2" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="AG3" s="2" t="inlineStr">
+      <c r="AK3" s="2" t="inlineStr">
         <is>
           <t>30.11</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Підготовчий етап</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Маркетингові дослідження і планування</t>
-        </is>
-      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Аналіз конкурентів і ринку футбольних товарів</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>01.06.2026</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>01.07.2026</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Виконано</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Власник</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Звіт із конкурентного аналізу</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n"/>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-      <c r="P4" s="5" t="n"/>
-      <c r="Q4" s="5" t="n"/>
-      <c r="R4" s="5" t="n"/>
-      <c r="S4" s="5" t="n"/>
-      <c r="T4" s="5" t="n"/>
-      <c r="U4" s="5" t="n"/>
-      <c r="V4" s="5" t="n"/>
-      <c r="W4" s="5" t="n"/>
-      <c r="X4" s="5" t="n"/>
-      <c r="Y4" s="5" t="n"/>
-      <c r="Z4" s="5" t="n"/>
-      <c r="AA4" s="5" t="n"/>
-      <c r="AB4" s="5" t="n"/>
-      <c r="AC4" s="5" t="n"/>
-      <c r="AD4" s="5" t="n"/>
-      <c r="AE4" s="5" t="n"/>
-      <c r="AF4" s="5" t="n"/>
-      <c r="AG4" s="5" t="n"/>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="6" t="n"/>
+      <c r="R4" s="6" t="n"/>
+      <c r="S4" s="6" t="n"/>
+      <c r="T4" s="6" t="n"/>
+      <c r="U4" s="6" t="n"/>
+      <c r="V4" s="6" t="n"/>
+      <c r="W4" s="6" t="n"/>
+      <c r="X4" s="6" t="n"/>
+      <c r="Y4" s="6" t="n"/>
+      <c r="Z4" s="6" t="n"/>
+      <c r="AA4" s="6" t="n"/>
+      <c r="AB4" s="6" t="n"/>
+      <c r="AC4" s="6" t="n"/>
+      <c r="AD4" s="6" t="n"/>
+      <c r="AE4" s="6" t="n"/>
+      <c r="AF4" s="6" t="n"/>
+      <c r="AG4" s="6" t="n"/>
+      <c r="AH4" s="6" t="n"/>
+      <c r="AI4" s="6" t="n"/>
+      <c r="AJ4" s="6" t="n"/>
+      <c r="AK4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Підготовчий етап</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Пошук та аналіз приміщень</t>
-        </is>
-      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>Визначення ЦА та концепції магазину</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>01.06.2026</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>01.07.2026</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>20.06.2026</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Виконано</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Власник / маркетолог</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Портрет ЦА, концепція точки</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n"/>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-      <c r="Y5" s="5" t="n"/>
-      <c r="Z5" s="5" t="n"/>
-      <c r="AA5" s="5" t="n"/>
-      <c r="AB5" s="5" t="n"/>
-      <c r="AC5" s="5" t="n"/>
-      <c r="AD5" s="5" t="n"/>
-      <c r="AE5" s="5" t="n"/>
-      <c r="AF5" s="5" t="n"/>
-      <c r="AG5" s="5" t="n"/>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n"/>
+      <c r="Q5" s="6" t="n"/>
+      <c r="R5" s="6" t="n"/>
+      <c r="S5" s="6" t="n"/>
+      <c r="T5" s="6" t="n"/>
+      <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="6" t="n"/>
+      <c r="Z5" s="6" t="n"/>
+      <c r="AA5" s="6" t="n"/>
+      <c r="AB5" s="6" t="n"/>
+      <c r="AC5" s="6" t="n"/>
+      <c r="AD5" s="6" t="n"/>
+      <c r="AE5" s="6" t="n"/>
+      <c r="AF5" s="6" t="n"/>
+      <c r="AG5" s="6" t="n"/>
+      <c r="AH5" s="6" t="n"/>
+      <c r="AI5" s="6" t="n"/>
+      <c r="AJ5" s="6" t="n"/>
+      <c r="AK5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Підготовчий етап</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Узгодження умов оренди</t>
-        </is>
-      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>Розробка фінансової моделі (CapEx/OpEx, окупність)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>У роботі</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Виконано</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Власник / фінконсультант</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Фінмодель XLSX зі сценаріями</t>
+        </is>
+      </c>
       <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
       <c r="N6" s="5" t="n"/>
       <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-      <c r="Y6" s="5" t="n"/>
-      <c r="Z6" s="5" t="n"/>
-      <c r="AA6" s="5" t="n"/>
-      <c r="AB6" s="5" t="n"/>
-      <c r="AC6" s="5" t="n"/>
-      <c r="AD6" s="5" t="n"/>
-      <c r="AE6" s="5" t="n"/>
-      <c r="AF6" s="5" t="n"/>
-      <c r="AG6" s="5" t="n"/>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="n"/>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="6" t="n"/>
+      <c r="T6" s="6" t="n"/>
+      <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
+      <c r="W6" s="6" t="n"/>
+      <c r="X6" s="6" t="n"/>
+      <c r="Y6" s="6" t="n"/>
+      <c r="Z6" s="6" t="n"/>
+      <c r="AA6" s="6" t="n"/>
+      <c r="AB6" s="6" t="n"/>
+      <c r="AC6" s="6" t="n"/>
+      <c r="AD6" s="6" t="n"/>
+      <c r="AE6" s="6" t="n"/>
+      <c r="AF6" s="6" t="n"/>
+      <c r="AG6" s="6" t="n"/>
+      <c r="AH6" s="6" t="n"/>
+      <c r="AI6" s="6" t="n"/>
+      <c r="AJ6" s="6" t="n"/>
+      <c r="AK6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Підготовка магазину</t>
-        </is>
+      <c r="A7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Ремонт і облаштування</t>
+          <t>Підготовчий етап</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>01.08.2026</t>
+          <t>Переговори з інвестором, узгодження term-sheet</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Заплановано</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>У роботі</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Власник / юрист</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Підписаний term-sheet</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="7" t="n"/>
+      <c r="N7" s="7" t="n"/>
       <c r="O7" s="7" t="n"/>
       <c r="P7" s="7" t="n"/>
       <c r="Q7" s="7" t="n"/>
-      <c r="R7" s="7" t="n"/>
-      <c r="S7" s="7" t="n"/>
-      <c r="T7" s="7" t="n"/>
-      <c r="U7" s="7" t="n"/>
-      <c r="V7" s="7" t="n"/>
-      <c r="W7" s="7" t="n"/>
-      <c r="X7" s="7" t="n"/>
-      <c r="Y7" s="5" t="n"/>
-      <c r="Z7" s="5" t="n"/>
-      <c r="AA7" s="5" t="n"/>
-      <c r="AB7" s="5" t="n"/>
-      <c r="AC7" s="5" t="n"/>
-      <c r="AD7" s="5" t="n"/>
-      <c r="AE7" s="5" t="n"/>
-      <c r="AF7" s="5" t="n"/>
-      <c r="AG7" s="5" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="6" t="n"/>
+      <c r="Z7" s="6" t="n"/>
+      <c r="AA7" s="6" t="n"/>
+      <c r="AB7" s="6" t="n"/>
+      <c r="AC7" s="6" t="n"/>
+      <c r="AD7" s="6" t="n"/>
+      <c r="AE7" s="6" t="n"/>
+      <c r="AF7" s="6" t="n"/>
+      <c r="AG7" s="6" t="n"/>
+      <c r="AH7" s="6" t="n"/>
+      <c r="AI7" s="6" t="n"/>
+      <c r="AJ7" s="6" t="n"/>
+      <c r="AK7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Підготовка магазину</t>
-        </is>
+      <c r="A8" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Закупівля обладнання та товару</t>
+          <t>Підготовчий етап</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>Пошук приміщень 40–60 м² (ТЦ / пішохідна вулиця)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>15.10.2026</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Заплановано</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
+          <t>01.06.2026</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Виконано</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Власник / рієлтор</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Шорт-ліст 3–5 локацій</t>
+        </is>
+      </c>
       <c r="K8" s="5" t="n"/>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="5" t="n"/>
       <c r="N8" s="5" t="n"/>
       <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="7" t="n"/>
-      <c r="U8" s="7" t="n"/>
-      <c r="V8" s="7" t="n"/>
-      <c r="W8" s="7" t="n"/>
-      <c r="X8" s="7" t="n"/>
-      <c r="Y8" s="7" t="n"/>
-      <c r="Z8" s="7" t="n"/>
-      <c r="AA8" s="5" t="n"/>
-      <c r="AB8" s="5" t="n"/>
-      <c r="AC8" s="5" t="n"/>
-      <c r="AD8" s="5" t="n"/>
-      <c r="AE8" s="5" t="n"/>
-      <c r="AF8" s="5" t="n"/>
-      <c r="AG8" s="5" t="n"/>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="6" t="n"/>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="6" t="n"/>
+      <c r="T8" s="6" t="n"/>
+      <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="6" t="n"/>
+      <c r="Z8" s="6" t="n"/>
+      <c r="AA8" s="6" t="n"/>
+      <c r="AB8" s="6" t="n"/>
+      <c r="AC8" s="6" t="n"/>
+      <c r="AD8" s="6" t="n"/>
+      <c r="AE8" s="6" t="n"/>
+      <c r="AF8" s="6" t="n"/>
+      <c r="AG8" s="6" t="n"/>
+      <c r="AH8" s="6" t="n"/>
+      <c r="AI8" s="6" t="n"/>
+      <c r="AJ8" s="6" t="n"/>
+      <c r="AK8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Підготовка магазину</t>
-        </is>
+      <c r="A9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Налаштування ІТ/ПРРО, інтеграція сайту</t>
+          <t>Підготовчий етап</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>Огляд локацій, аналіз пішохідного трафіку</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>31.10.2026</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Заплановано</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>05.07.2026</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Виконано</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Власник</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Обрана локація</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="5" t="n"/>
       <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="7" t="n"/>
-      <c r="W9" s="7" t="n"/>
-      <c r="X9" s="7" t="n"/>
-      <c r="Y9" s="7" t="n"/>
-      <c r="Z9" s="7" t="n"/>
-      <c r="AA9" s="7" t="n"/>
-      <c r="AB9" s="7" t="n"/>
-      <c r="AC9" s="5" t="n"/>
-      <c r="AD9" s="5" t="n"/>
-      <c r="AE9" s="5" t="n"/>
-      <c r="AF9" s="5" t="n"/>
-      <c r="AG9" s="5" t="n"/>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="6" t="n"/>
+      <c r="R9" s="6" t="n"/>
+      <c r="S9" s="6" t="n"/>
+      <c r="T9" s="6" t="n"/>
+      <c r="U9" s="6" t="n"/>
+      <c r="V9" s="6" t="n"/>
+      <c r="W9" s="6" t="n"/>
+      <c r="X9" s="6" t="n"/>
+      <c r="Y9" s="6" t="n"/>
+      <c r="Z9" s="6" t="n"/>
+      <c r="AA9" s="6" t="n"/>
+      <c r="AB9" s="6" t="n"/>
+      <c r="AC9" s="6" t="n"/>
+      <c r="AD9" s="6" t="n"/>
+      <c r="AE9" s="6" t="n"/>
+      <c r="AF9" s="6" t="n"/>
+      <c r="AG9" s="6" t="n"/>
+      <c r="AH9" s="6" t="n"/>
+      <c r="AI9" s="6" t="n"/>
+      <c r="AJ9" s="6" t="n"/>
+      <c r="AK9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Підготовчий етап</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Юридична перевірка договору оренди</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>У роботі</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Юрист</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Висновок юриста, правки до договору</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="7" t="n"/>
+      <c r="P10" s="7" t="n"/>
+      <c r="Q10" s="6" t="n"/>
+      <c r="R10" s="6" t="n"/>
+      <c r="S10" s="6" t="n"/>
+      <c r="T10" s="6" t="n"/>
+      <c r="U10" s="6" t="n"/>
+      <c r="V10" s="6" t="n"/>
+      <c r="W10" s="6" t="n"/>
+      <c r="X10" s="6" t="n"/>
+      <c r="Y10" s="6" t="n"/>
+      <c r="Z10" s="6" t="n"/>
+      <c r="AA10" s="6" t="n"/>
+      <c r="AB10" s="6" t="n"/>
+      <c r="AC10" s="6" t="n"/>
+      <c r="AD10" s="6" t="n"/>
+      <c r="AE10" s="6" t="n"/>
+      <c r="AF10" s="6" t="n"/>
+      <c r="AG10" s="6" t="n"/>
+      <c r="AH10" s="6" t="n"/>
+      <c r="AI10" s="6" t="n"/>
+      <c r="AJ10" s="6" t="n"/>
+      <c r="AK10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Підготовчий етап</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Підписання договору оренди</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Власник</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Договір оренди + завдаток</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="6" t="n"/>
+      <c r="S11" s="6" t="n"/>
+      <c r="T11" s="6" t="n"/>
+      <c r="U11" s="6" t="n"/>
+      <c r="V11" s="6" t="n"/>
+      <c r="W11" s="6" t="n"/>
+      <c r="X11" s="6" t="n"/>
+      <c r="Y11" s="6" t="n"/>
+      <c r="Z11" s="6" t="n"/>
+      <c r="AA11" s="6" t="n"/>
+      <c r="AB11" s="6" t="n"/>
+      <c r="AC11" s="6" t="n"/>
+      <c r="AD11" s="6" t="n"/>
+      <c r="AE11" s="6" t="n"/>
+      <c r="AF11" s="6" t="n"/>
+      <c r="AG11" s="6" t="n"/>
+      <c r="AH11" s="6" t="n"/>
+      <c r="AI11" s="6" t="n"/>
+      <c r="AJ11" s="6" t="n"/>
+      <c r="AK11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Юридичне оформлення</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Реєстрація нового ТОВ (SPV) для офлайн-точки</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>01.08.2026</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>15.08.2026</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Юрист</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Виписка з ЄДР, статут</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="n"/>
+      <c r="R12" s="6" t="n"/>
+      <c r="S12" s="8" t="n"/>
+      <c r="T12" s="8" t="n"/>
+      <c r="U12" s="8" t="n"/>
+      <c r="V12" s="6" t="n"/>
+      <c r="W12" s="6" t="n"/>
+      <c r="X12" s="6" t="n"/>
+      <c r="Y12" s="6" t="n"/>
+      <c r="Z12" s="6" t="n"/>
+      <c r="AA12" s="6" t="n"/>
+      <c r="AB12" s="6" t="n"/>
+      <c r="AC12" s="6" t="n"/>
+      <c r="AD12" s="6" t="n"/>
+      <c r="AE12" s="6" t="n"/>
+      <c r="AF12" s="6" t="n"/>
+      <c r="AG12" s="6" t="n"/>
+      <c r="AH12" s="6" t="n"/>
+      <c r="AI12" s="6" t="n"/>
+      <c r="AJ12" s="6" t="n"/>
+      <c r="AK12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Юридичне оформлення</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Відкриття банківського рахунку, еквайринг</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>15.08.2026</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Власник</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Рахунок + POS-термінал банку</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="6" t="n"/>
+      <c r="R13" s="6" t="n"/>
+      <c r="S13" s="6" t="n"/>
+      <c r="T13" s="6" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="6" t="n"/>
+      <c r="Y13" s="6" t="n"/>
+      <c r="Z13" s="6" t="n"/>
+      <c r="AA13" s="6" t="n"/>
+      <c r="AB13" s="6" t="n"/>
+      <c r="AC13" s="6" t="n"/>
+      <c r="AD13" s="6" t="n"/>
+      <c r="AE13" s="6" t="n"/>
+      <c r="AF13" s="6" t="n"/>
+      <c r="AG13" s="6" t="n"/>
+      <c r="AH13" s="6" t="n"/>
+      <c r="AI13" s="6" t="n"/>
+      <c r="AJ13" s="6" t="n"/>
+      <c r="AK13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Юридичне оформлення</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Підписання інвестиційного договору (позика/SPV)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>01.08.2026</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Юрист / інвестор</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Інвестдоговір, надходження 1-го траншу</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="6" t="n"/>
+      <c r="R14" s="6" t="n"/>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="6" t="n"/>
+      <c r="Z14" s="6" t="n"/>
+      <c r="AA14" s="6" t="n"/>
+      <c r="AB14" s="6" t="n"/>
+      <c r="AC14" s="6" t="n"/>
+      <c r="AD14" s="6" t="n"/>
+      <c r="AE14" s="6" t="n"/>
+      <c r="AF14" s="6" t="n"/>
+      <c r="AG14" s="6" t="n"/>
+      <c r="AH14" s="6" t="n"/>
+      <c r="AI14" s="6" t="n"/>
+      <c r="AJ14" s="6" t="n"/>
+      <c r="AK14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Підготовка магазину</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Дизайн-проєкт торгового залу та фасаду</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>01.08.2026</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Дизайнер</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Дизайн-проєкт, кошторис ремонту</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="8" t="n"/>
+      <c r="R15" s="8" t="n"/>
+      <c r="S15" s="8" t="n"/>
+      <c r="T15" s="6" t="n"/>
+      <c r="U15" s="6" t="n"/>
+      <c r="V15" s="6" t="n"/>
+      <c r="W15" s="6" t="n"/>
+      <c r="X15" s="6" t="n"/>
+      <c r="Y15" s="6" t="n"/>
+      <c r="Z15" s="6" t="n"/>
+      <c r="AA15" s="6" t="n"/>
+      <c r="AB15" s="6" t="n"/>
+      <c r="AC15" s="6" t="n"/>
+      <c r="AD15" s="6" t="n"/>
+      <c r="AE15" s="6" t="n"/>
+      <c r="AF15" s="6" t="n"/>
+      <c r="AG15" s="6" t="n"/>
+      <c r="AH15" s="6" t="n"/>
+      <c r="AI15" s="6" t="n"/>
+      <c r="AJ15" s="6" t="n"/>
+      <c r="AK15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Підготовка магазину</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Ремонтні роботи у приміщенні</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>01.08.2026</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Підрядник</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Готове приміщення</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="6" t="n"/>
+      <c r="R16" s="6" t="n"/>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="8" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="6" t="n"/>
+      <c r="AB16" s="6" t="n"/>
+      <c r="AC16" s="6" t="n"/>
+      <c r="AD16" s="6" t="n"/>
+      <c r="AE16" s="6" t="n"/>
+      <c r="AF16" s="6" t="n"/>
+      <c r="AG16" s="6" t="n"/>
+      <c r="AH16" s="6" t="n"/>
+      <c r="AI16" s="6" t="n"/>
+      <c r="AJ16" s="6" t="n"/>
+      <c r="AK16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Підготовка магазину</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Виготовлення/монтаж стелажів, вивіски, освітлення</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>01.09.2026</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Підрядник</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Обладнаний торговий зал</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="6" t="n"/>
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="6" t="n"/>
+      <c r="T17" s="6" t="n"/>
+      <c r="U17" s="6" t="n"/>
+      <c r="V17" s="6" t="n"/>
+      <c r="W17" s="6" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="6" t="n"/>
+      <c r="AD17" s="6" t="n"/>
+      <c r="AE17" s="6" t="n"/>
+      <c r="AF17" s="6" t="n"/>
+      <c r="AG17" s="6" t="n"/>
+      <c r="AH17" s="6" t="n"/>
+      <c r="AI17" s="6" t="n"/>
+      <c r="AJ17" s="6" t="n"/>
+      <c r="AK17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Підготовка магазину</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Договори з постачальниками (Nike, Adidas, Joma та ін.)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>01.08.2026</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>01.09.2026</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Власник</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Підписані договори постачання</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="6" t="n"/>
+      <c r="R18" s="6" t="n"/>
+      <c r="S18" s="8" t="n"/>
+      <c r="T18" s="8" t="n"/>
+      <c r="U18" s="8" t="n"/>
+      <c r="V18" s="8" t="n"/>
+      <c r="W18" s="8" t="n"/>
+      <c r="X18" s="8" t="n"/>
+      <c r="Y18" s="6" t="n"/>
+      <c r="Z18" s="6" t="n"/>
+      <c r="AA18" s="6" t="n"/>
+      <c r="AB18" s="6" t="n"/>
+      <c r="AC18" s="6" t="n"/>
+      <c r="AD18" s="6" t="n"/>
+      <c r="AE18" s="6" t="n"/>
+      <c r="AF18" s="6" t="n"/>
+      <c r="AG18" s="6" t="n"/>
+      <c r="AH18" s="6" t="n"/>
+      <c r="AI18" s="6" t="n"/>
+      <c r="AJ18" s="6" t="n"/>
+      <c r="AK18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Підготовка магазину</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Закупівля торгового обладнання і каси</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>01.09.2026</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Власник</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Комп'ютер, принтер чеків, сканер</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="n"/>
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="6" t="n"/>
+      <c r="T19" s="6" t="n"/>
+      <c r="U19" s="6" t="n"/>
+      <c r="V19" s="6" t="n"/>
+      <c r="W19" s="6" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="6" t="n"/>
+      <c r="AB19" s="6" t="n"/>
+      <c r="AC19" s="6" t="n"/>
+      <c r="AD19" s="6" t="n"/>
+      <c r="AE19" s="6" t="n"/>
+      <c r="AF19" s="6" t="n"/>
+      <c r="AG19" s="6" t="n"/>
+      <c r="AH19" s="6" t="n"/>
+      <c r="AI19" s="6" t="n"/>
+      <c r="AJ19" s="6" t="n"/>
+      <c r="AK19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Підготовка магазину</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Закупівля початкового товарного запасу</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>15.10.2026</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Власник</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Товар на складі магазину</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n"/>
+      <c r="Q20" s="6" t="n"/>
+      <c r="R20" s="6" t="n"/>
+      <c r="S20" s="6" t="n"/>
+      <c r="T20" s="6" t="n"/>
+      <c r="U20" s="6" t="n"/>
+      <c r="V20" s="6" t="n"/>
+      <c r="W20" s="6" t="n"/>
+      <c r="X20" s="6" t="n"/>
+      <c r="Y20" s="6" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="6" t="n"/>
+      <c r="AF20" s="6" t="n"/>
+      <c r="AG20" s="6" t="n"/>
+      <c r="AH20" s="6" t="n"/>
+      <c r="AI20" s="6" t="n"/>
+      <c r="AJ20" s="6" t="n"/>
+      <c r="AK20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>ІТ та інтеграції</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Вибір і впровадження ERP/CRM (Dilovod/Odoo/KeyCRM)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>01.09.2026</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>01.10.2026</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>ІТ-підрядник</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Працююча система обліку</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="6" t="n"/>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="6" t="n"/>
+      <c r="R21" s="6" t="n"/>
+      <c r="S21" s="6" t="n"/>
+      <c r="T21" s="6" t="n"/>
+      <c r="U21" s="6" t="n"/>
+      <c r="V21" s="6" t="n"/>
+      <c r="W21" s="6" t="n"/>
+      <c r="X21" s="8" t="n"/>
+      <c r="Y21" s="8" t="n"/>
+      <c r="Z21" s="8" t="n"/>
+      <c r="AA21" s="8" t="n"/>
+      <c r="AB21" s="8" t="n"/>
+      <c r="AC21" s="6" t="n"/>
+      <c r="AD21" s="6" t="n"/>
+      <c r="AE21" s="6" t="n"/>
+      <c r="AF21" s="6" t="n"/>
+      <c r="AG21" s="6" t="n"/>
+      <c r="AH21" s="6" t="n"/>
+      <c r="AI21" s="6" t="n"/>
+      <c r="AJ21" s="6" t="n"/>
+      <c r="AK21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>ІТ та інтеграції</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Реєстрація і налаштування ПРРО (Checkbox)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>01.10.2026</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Бухгалтер / ІТ</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Фіскалізація, тестовий чек, Z-звіт</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="n"/>
+      <c r="R22" s="6" t="n"/>
+      <c r="S22" s="6" t="n"/>
+      <c r="T22" s="6" t="n"/>
+      <c r="U22" s="6" t="n"/>
+      <c r="V22" s="6" t="n"/>
+      <c r="W22" s="6" t="n"/>
+      <c r="X22" s="6" t="n"/>
+      <c r="Y22" s="6" t="n"/>
+      <c r="Z22" s="8" t="n"/>
+      <c r="AA22" s="8" t="n"/>
+      <c r="AB22" s="8" t="n"/>
+      <c r="AC22" s="6" t="n"/>
+      <c r="AD22" s="6" t="n"/>
+      <c r="AE22" s="6" t="n"/>
+      <c r="AF22" s="6" t="n"/>
+      <c r="AG22" s="6" t="n"/>
+      <c r="AH22" s="6" t="n"/>
+      <c r="AI22" s="6" t="n"/>
+      <c r="AJ22" s="6" t="n"/>
+      <c r="AK22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>ІТ та інтеграції</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Інтеграція сайту з обліком залишків (API)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>31.10.2026</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Програміст</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Єдині залишки онлайн/офлайн</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="6" t="n"/>
+      <c r="R23" s="6" t="n"/>
+      <c r="S23" s="6" t="n"/>
+      <c r="T23" s="6" t="n"/>
+      <c r="U23" s="6" t="n"/>
+      <c r="V23" s="6" t="n"/>
+      <c r="W23" s="6" t="n"/>
+      <c r="X23" s="6" t="n"/>
+      <c r="Y23" s="6" t="n"/>
+      <c r="Z23" s="8" t="n"/>
+      <c r="AA23" s="8" t="n"/>
+      <c r="AB23" s="8" t="n"/>
+      <c r="AC23" s="8" t="n"/>
+      <c r="AD23" s="8" t="n"/>
+      <c r="AE23" s="8" t="n"/>
+      <c r="AF23" s="8" t="n"/>
+      <c r="AG23" s="6" t="n"/>
+      <c r="AH23" s="6" t="n"/>
+      <c r="AI23" s="6" t="n"/>
+      <c r="AJ23" s="6" t="n"/>
+      <c r="AK23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>ІТ та інтеграції</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Налаштування єдиної бонусної програми</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>01.10.2026</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>31.10.2026</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Програміст / маркетолог</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Спільний акаунт клієнта</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="6" t="n"/>
+      <c r="Q24" s="6" t="n"/>
+      <c r="R24" s="6" t="n"/>
+      <c r="S24" s="6" t="n"/>
+      <c r="T24" s="6" t="n"/>
+      <c r="U24" s="6" t="n"/>
+      <c r="V24" s="6" t="n"/>
+      <c r="W24" s="6" t="n"/>
+      <c r="X24" s="6" t="n"/>
+      <c r="Y24" s="6" t="n"/>
+      <c r="Z24" s="6" t="n"/>
+      <c r="AA24" s="6" t="n"/>
+      <c r="AB24" s="8" t="n"/>
+      <c r="AC24" s="8" t="n"/>
+      <c r="AD24" s="8" t="n"/>
+      <c r="AE24" s="8" t="n"/>
+      <c r="AF24" s="8" t="n"/>
+      <c r="AG24" s="6" t="n"/>
+      <c r="AH24" s="6" t="n"/>
+      <c r="AI24" s="6" t="n"/>
+      <c r="AJ24" s="6" t="n"/>
+      <c r="AK24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Персонал</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Публікація вакансій, співбесіди (2 продавці)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>01.10.2026</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>15.10.2026</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Власник</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2 кандидати прийняті</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="6" t="n"/>
+      <c r="Q25" s="6" t="n"/>
+      <c r="R25" s="6" t="n"/>
+      <c r="S25" s="6" t="n"/>
+      <c r="T25" s="6" t="n"/>
+      <c r="U25" s="6" t="n"/>
+      <c r="V25" s="6" t="n"/>
+      <c r="W25" s="6" t="n"/>
+      <c r="X25" s="6" t="n"/>
+      <c r="Y25" s="6" t="n"/>
+      <c r="Z25" s="6" t="n"/>
+      <c r="AA25" s="6" t="n"/>
+      <c r="AB25" s="8" t="n"/>
+      <c r="AC25" s="8" t="n"/>
+      <c r="AD25" s="8" t="n"/>
+      <c r="AE25" s="6" t="n"/>
+      <c r="AF25" s="6" t="n"/>
+      <c r="AG25" s="6" t="n"/>
+      <c r="AH25" s="6" t="n"/>
+      <c r="AI25" s="6" t="n"/>
+      <c r="AJ25" s="6" t="n"/>
+      <c r="AK25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Персонал</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Навчання персоналу (товар, каса, сервіс)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>15.10.2026</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>01.11.2026</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Власник</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Навчені співробітники</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
+      <c r="N26" s="6" t="n"/>
+      <c r="O26" s="6" t="n"/>
+      <c r="P26" s="6" t="n"/>
+      <c r="Q26" s="6" t="n"/>
+      <c r="R26" s="6" t="n"/>
+      <c r="S26" s="6" t="n"/>
+      <c r="T26" s="6" t="n"/>
+      <c r="U26" s="6" t="n"/>
+      <c r="V26" s="6" t="n"/>
+      <c r="W26" s="6" t="n"/>
+      <c r="X26" s="6" t="n"/>
+      <c r="Y26" s="6" t="n"/>
+      <c r="Z26" s="6" t="n"/>
+      <c r="AA26" s="6" t="n"/>
+      <c r="AB26" s="6" t="n"/>
+      <c r="AC26" s="6" t="n"/>
+      <c r="AD26" s="8" t="n"/>
+      <c r="AE26" s="8" t="n"/>
+      <c r="AF26" s="8" t="n"/>
+      <c r="AG26" s="6" t="n"/>
+      <c r="AH26" s="6" t="n"/>
+      <c r="AI26" s="6" t="n"/>
+      <c r="AJ26" s="6" t="n"/>
+      <c r="AK26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Запуск</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Набір та навчання персоналу</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>01.10.2026</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Мерчандайзинг, викладка товару</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Персонал / власник</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Оформлений торговий зал</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n"/>
+      <c r="M27" s="6" t="n"/>
+      <c r="N27" s="6" t="n"/>
+      <c r="O27" s="6" t="n"/>
+      <c r="P27" s="6" t="n"/>
+      <c r="Q27" s="6" t="n"/>
+      <c r="R27" s="6" t="n"/>
+      <c r="S27" s="6" t="n"/>
+      <c r="T27" s="6" t="n"/>
+      <c r="U27" s="6" t="n"/>
+      <c r="V27" s="6" t="n"/>
+      <c r="W27" s="6" t="n"/>
+      <c r="X27" s="6" t="n"/>
+      <c r="Y27" s="6" t="n"/>
+      <c r="Z27" s="6" t="n"/>
+      <c r="AA27" s="6" t="n"/>
+      <c r="AB27" s="6" t="n"/>
+      <c r="AC27" s="6" t="n"/>
+      <c r="AD27" s="6" t="n"/>
+      <c r="AE27" s="8" t="n"/>
+      <c r="AF27" s="8" t="n"/>
+      <c r="AG27" s="8" t="n"/>
+      <c r="AH27" s="6" t="n"/>
+      <c r="AI27" s="6" t="n"/>
+      <c r="AJ27" s="6" t="n"/>
+      <c r="AK27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Запуск</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Рекламна кампанія до відкриття (SMM, локальна реклама)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>15.11.2026</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Заплановано</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Маркетолог</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Анонси, охоплення ЦА</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
+      <c r="N28" s="6" t="n"/>
+      <c r="O28" s="6" t="n"/>
+      <c r="P28" s="6" t="n"/>
+      <c r="Q28" s="6" t="n"/>
+      <c r="R28" s="6" t="n"/>
+      <c r="S28" s="6" t="n"/>
+      <c r="T28" s="6" t="n"/>
+      <c r="U28" s="6" t="n"/>
+      <c r="V28" s="6" t="n"/>
+      <c r="W28" s="6" t="n"/>
+      <c r="X28" s="6" t="n"/>
+      <c r="Y28" s="6" t="n"/>
+      <c r="Z28" s="6" t="n"/>
+      <c r="AA28" s="6" t="n"/>
+      <c r="AB28" s="6" t="n"/>
+      <c r="AC28" s="6" t="n"/>
+      <c r="AD28" s="6" t="n"/>
+      <c r="AE28" s="8" t="n"/>
+      <c r="AF28" s="8" t="n"/>
+      <c r="AG28" s="8" t="n"/>
+      <c r="AH28" s="8" t="n"/>
+      <c r="AI28" s="6" t="n"/>
+      <c r="AJ28" s="6" t="n"/>
+      <c r="AK28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Запуск</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Тестовий запуск (soft opening)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>01.11.2026</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>14.11.2026</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Заплановано</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="5" t="n"/>
-      <c r="V10" s="5" t="n"/>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="7" t="n"/>
-      <c r="Y10" s="7" t="n"/>
-      <c r="Z10" s="7" t="n"/>
-      <c r="AA10" s="7" t="n"/>
-      <c r="AB10" s="7" t="n"/>
-      <c r="AC10" s="5" t="n"/>
-      <c r="AD10" s="5" t="n"/>
-      <c r="AE10" s="5" t="n"/>
-      <c r="AF10" s="5" t="n"/>
-      <c r="AG10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Уся команда</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Відпрацьовані процеси продажу</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="n"/>
+      <c r="N29" s="6" t="n"/>
+      <c r="O29" s="6" t="n"/>
+      <c r="P29" s="6" t="n"/>
+      <c r="Q29" s="6" t="n"/>
+      <c r="R29" s="6" t="n"/>
+      <c r="S29" s="6" t="n"/>
+      <c r="T29" s="6" t="n"/>
+      <c r="U29" s="6" t="n"/>
+      <c r="V29" s="6" t="n"/>
+      <c r="W29" s="6" t="n"/>
+      <c r="X29" s="6" t="n"/>
+      <c r="Y29" s="6" t="n"/>
+      <c r="Z29" s="6" t="n"/>
+      <c r="AA29" s="6" t="n"/>
+      <c r="AB29" s="6" t="n"/>
+      <c r="AC29" s="6" t="n"/>
+      <c r="AD29" s="6" t="n"/>
+      <c r="AE29" s="6" t="n"/>
+      <c r="AF29" s="8" t="n"/>
+      <c r="AG29" s="8" t="n"/>
+      <c r="AH29" s="8" t="n"/>
+      <c r="AI29" s="6" t="n"/>
+      <c r="AJ29" s="6" t="n"/>
+      <c r="AK29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Запуск</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Тестовий запуск і реклама</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>01.11.2026</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>УРОЧИСТЕ ВІДКРИТТЯ МАГАЗИНУ</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>15.11.2026</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>15.11.2026</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>ВІХА</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Уся команда</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>Старт повноцінних продажів</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="n"/>
+      <c r="N30" s="6" t="n"/>
+      <c r="O30" s="6" t="n"/>
+      <c r="P30" s="6" t="n"/>
+      <c r="Q30" s="6" t="n"/>
+      <c r="R30" s="6" t="n"/>
+      <c r="S30" s="6" t="n"/>
+      <c r="T30" s="6" t="n"/>
+      <c r="U30" s="6" t="n"/>
+      <c r="V30" s="6" t="n"/>
+      <c r="W30" s="6" t="n"/>
+      <c r="X30" s="6" t="n"/>
+      <c r="Y30" s="6" t="n"/>
+      <c r="Z30" s="6" t="n"/>
+      <c r="AA30" s="6" t="n"/>
+      <c r="AB30" s="6" t="n"/>
+      <c r="AC30" s="6" t="n"/>
+      <c r="AD30" s="6" t="n"/>
+      <c r="AE30" s="6" t="n"/>
+      <c r="AF30" s="6" t="n"/>
+      <c r="AG30" s="6" t="n"/>
+      <c r="AH30" s="11" t="n"/>
+      <c r="AI30" s="6" t="n"/>
+      <c r="AJ30" s="6" t="n"/>
+      <c r="AK30" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Легенда:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Виконано</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>У роботі</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n"/>
+      <c r="B35" t="inlineStr">
         <is>
           <t>Заплановано</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="5" t="n"/>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-      <c r="Y11" s="5" t="n"/>
-      <c r="Z11" s="5" t="n"/>
-      <c r="AA11" s="5" t="n"/>
-      <c r="AB11" s="7" t="n"/>
-      <c r="AC11" s="7" t="n"/>
-      <c r="AD11" s="7" t="n"/>
-      <c r="AE11" s="5" t="n"/>
-      <c r="AF11" s="5" t="n"/>
-      <c r="AG11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Запуск</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Відкриття магазину</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>15.11.2026</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>15.11.2026</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>ВІХА</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-      <c r="Y12" s="5" t="n"/>
-      <c r="Z12" s="5" t="n"/>
-      <c r="AA12" s="5" t="n"/>
-      <c r="AB12" s="5" t="n"/>
-      <c r="AC12" s="5" t="n"/>
-      <c r="AD12" s="8" t="n"/>
-      <c r="AE12" s="5" t="n"/>
-      <c r="AF12" s="5" t="n"/>
-      <c r="AG12" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Легенда:</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Виконано</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>У роботі</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Заплановано</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" t="inlineStr">
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" t="inlineStr">
         <is>
           <t>Віха (відкриття)</t>
         </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Сумарний бюджет етапів за планом:</t>
+        </is>
+      </c>
+      <c r="B38" s="13">
+        <f>SUM(I4:I30)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1266,192 +2770,416 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Ключові віхи проєкту</t>
+          <t>Ключові віхи проєкту з критеріями готовності</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Етап</t>
+          <t>Віха</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Період</t>
+          <t>Дата</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Результат</t>
+          <t>Зміст</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Критерій готовності (Definition of Done)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Маркетингові дослідження і планування</t>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>М1. Завершено дослідження ринку</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>червень–липень 2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Підтверджена концепція, ЦА, асортимент</t>
+          <t>Звіт з аналізу конкурентів, портрет ЦА, фінмодель</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Є документи: конкурентний аналіз, фінмодель XLSX; інвестору надіслано матеріали</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Пошук та аналіз приміщень</t>
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>М2. Підписано договір оренди</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>червень–липень 2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Шорт-ліст локацій (40–50 м²)</t>
+          <t>Договір оренди приміщення 40–60 м²</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Договір підписано, завдаток сплачено, отримано ключі/доступ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Узгодження умов оренди</t>
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>М3. Підписано інвестиційний договір</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>липень 2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Підписаний договір оренди</t>
+          <t>Term-sheet → інвестдоговір, 1-й транш</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Кошти 1-го траншу надійшли на рахунок нового ТОВ</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Ремонт і облаштування</t>
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>М4. Зареєстровано нове ТОВ і рахунок</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>серпень–вересень 2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Готовий торговий зал, стелажі, фасад</t>
+          <t>ЄДР, статут, банківський рахунок, еквайринг</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Виписка з ЄДР; рахунок активний; POS-термінал замовлено</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Закупівля обладнання та товару</t>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>М5. Приміщення готове</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>вересень–жовтень 2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Початковий товарний запас, каса, техніка</t>
+          <t>Ремонт завершено, стелажі та вивіска змонтовані</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Акт виконаних робіт; зал готовий до викладки товару</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Налаштування ІТ/ПРРО, інтеграція сайту</t>
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>М6. Товар і обладнання на місці</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>вересень–жовтень 2026</t>
+          <t>15.10.2026</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Єдиний облік залишків онлайн/офлайн, ПРРО</t>
+          <t>Початковий запас ~300 тис. грн, каса, техніка</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Товар оприбутковано в обліковій системі; каса працює</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Набір та навчання персоналу</t>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>М7. ІТ-контур запущено</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>жовтень 2026</t>
+          <t>31.10.2026</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2 навчені співробітники</t>
+          <t>ERP/CRM + ПРРО Checkbox + інтеграція з сайтом</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Тестовий продаж пробито через ПРРО; залишки синхронізуються із сайтом</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Тестовий запуск і реклама</t>
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>М8. Персонал готовий</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>перша половина листопада 2026</t>
+          <t>01.11.2026</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Відпрацьовані процеси, прогрітий трафік</t>
+          <t>2 співробітники найняті та навчені</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Складено графік змін; персонал склав внутрішній тест із товару й каси</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>ОФІЦІЙНЕ ВІДКРИТТЯ МАГАЗИНУ</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>15 листопада 2026</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Старт продажів</t>
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>М9. Soft opening пройдено</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>14.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Два тижні тестових продажів</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Зібрано перший зворотний зв'язок; усунуто збої процесів</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>М10. ОФІЦІЙНЕ ВІДКРИТТЯ</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>15.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Урочисте відкриття, старт повноцінних продажів</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Проведено акцію відкриття; перший день продажів закрито Z-звітом</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Помісячний план робіт (зведення)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Місяць</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Роботи</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Результати місяця</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Червень 2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Аналіз ринку і конкурентів; визначення ЦА; фінмодель; старт переговорів з інвестором; пошук приміщень</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Звіт з аналізу; шорт-ліст локацій; чернетка term-sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Липень 2026</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Узгодження term-sheet; юрперевірка та підписання оренди; дизайн-проєкт залу</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Договір оренди; дизайн-проєкт; кошторис ремонту</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Серпень 2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Реєстрація ТОВ (SPV); банк/еквайринг; інвестдоговір і 1-й транш; старт ремонту; договори з постачальниками</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Нове ТОВ; кошти на рахунку; ремонт у процесі</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Вересень 2026</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Завершення ремонту; стелажі/вивіска; закупівля обладнання; старт закупівлі товару; впровадження ERP/CRM; реєстрація ПРРО</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Готовий зал; каса і техніка на місці; ПРРО зареєстровано</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Жовтень 2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Завершення закупівлі товару; інтеграція сайту з обліком; бонусна програма; найм і навчання персоналу; старт реклами</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Товар оприбутковано; ІТ-контур працює; персонал навчений</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Листопад 2026</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Мерчандайзинг; soft opening (1–14.11); рекламна кампанія; УРОЧИСТЕ ВІДКРИТТЯ 15.11</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Магазин відкрито; перші продажі; Z-звіти щодня</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Діаграма_Ганта.xlsx
+++ b/Діаграма_Ганта.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +38,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -104,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,6 +132,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -497,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK38"/>
+  <dimension ref="A1:AK39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -508,7 +512,7 @@
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
     <col width="5.5" customWidth="1" min="11" max="11"/>
     <col width="5.5" customWidth="1" min="12" max="12"/>
@@ -542,7 +546,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Дорожня карта відкриття фізичного магазину footballshop.com.ua (2026) — детальний план</t>
+          <t>Дорожня карта відкриття фізичного магазину footballshop.com.ua (2026) — детальний план, ціни 2026</t>
         </is>
       </c>
     </row>
@@ -990,7 +994,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>15000</v>
+        <v>50000</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1209,7 +1213,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10000</v>
+        <v>35000</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1282,11 +1286,11 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>50000</v>
+        <v>180000</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Договір оренди + завдаток</t>
+          <t>Договір оренди + завдаток (2 міс.)</t>
         </is>
       </c>
       <c r="K11" s="6" t="n"/>
@@ -1355,7 +1359,7 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>10000</v>
+        <v>35000</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1501,7 +1505,7 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1578,7 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>25000</v>
+        <v>90000</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1647,7 +1651,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>150000</v>
+        <v>550000</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1720,7 +1724,7 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>50000</v>
+        <v>180000</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1866,7 +1870,7 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>50000</v>
+        <v>175000</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1939,7 +1943,7 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>300000</v>
+        <v>1100000</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -2012,7 +2016,7 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2085,7 +2089,7 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2158,7 +2162,7 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>40000</v>
+        <v>140000</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2231,7 +2235,7 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>15000</v>
+        <v>50000</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2304,7 +2308,7 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2377,7 +2381,7 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2523,7 +2527,7 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>30000</v>
+        <v>110000</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2671,7 +2675,7 @@
         </is>
       </c>
       <c r="I30" s="10" t="n">
-        <v>10000</v>
+        <v>35000</v>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
@@ -2756,6 +2760,13 @@
         <v/>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>(≈ 2,9 млн грн — узгоджується з CapEx 2,4–3,7 млн грн у фінмоделі)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -2809,7 +2820,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>М1. Завершено дослідження ринку</t>
         </is>
@@ -2831,7 +2842,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>М2. Підписано договір оренди</t>
         </is>
@@ -2853,7 +2864,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>М3. Підписано інвестиційний договір</t>
         </is>
@@ -2875,7 +2886,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>М4. Зареєстровано нове ТОВ і рахунок</t>
         </is>
@@ -2897,7 +2908,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>М5. Приміщення готове</t>
         </is>
@@ -2919,7 +2930,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>М6. Товар і обладнання на місці</t>
         </is>
@@ -2931,7 +2942,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Початковий запас ~300 тис. грн, каса, техніка</t>
+          <t>Початковий запас ~1,1 млн грн, каса, техніка</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -2941,7 +2952,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>М7. ІТ-контур запущено</t>
         </is>
@@ -2963,7 +2974,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>М8. Персонал готовий</t>
         </is>
@@ -2985,7 +2996,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>М9. Soft opening пройдено</t>
         </is>
@@ -3007,7 +3018,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>М10. ОФІЦІЙНЕ ВІДКРИТТЯ</t>
         </is>
@@ -3075,7 +3086,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Червень 2026</t>
         </is>
@@ -3092,7 +3103,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Липень 2026</t>
         </is>
@@ -3109,7 +3120,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Серпень 2026</t>
         </is>
@@ -3126,7 +3137,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Вересень 2026</t>
         </is>
@@ -3143,7 +3154,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Жовтень 2026</t>
         </is>
@@ -3160,7 +3171,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Листопад 2026</t>
         </is>

--- a/Діаграма_Ганта.xlsx
+++ b/Діаграма_Ганта.xlsx
@@ -546,7 +546,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Дорожня карта відкриття фізичного магазину footballshop.com.ua (2026) — детальний план, ціни 2026</t>
+          <t>Дорожня карта відкриття фізичного магазину footballshop.com.ua (2026) — детальний план</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>(≈ 2,9 млн грн — узгоджується з CapEx 2,4–3,7 млн грн у фінмоделі)</t>
+          <t>(≈ 2,9 млн грн — узгоджується з CapEx 2,3–3,7 млн грн у фінмоделі)</t>
         </is>
       </c>
     </row>
